--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\Cyber\Demo-Cyber\MiniTemplate\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D61F84-F9C2-461A-A5CB-0995CD1F5125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28785" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="86">
   <si>
     <t>##var</t>
   </si>
@@ -57,6 +53,15 @@
     <t>icon</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>usable</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -87,9 +92,54 @@
     <t>来源</t>
   </si>
   <si>
+    <t>主要用途</t>
+  </si>
+  <si>
     <t>图片路径</t>
   </si>
   <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>可使用</t>
+  </si>
+  <si>
+    <t>物品品阶</t>
+  </si>
+  <si>
+    <t>灵晶微体</t>
+  </si>
+  <si>
+    <t>菱形晶体内部闪耀着变幻莫测的色彩，可以兑换少量灵晶币。</t>
+  </si>
+  <si>
+    <t>广泛</t>
+  </si>
+  <si>
+    <t>兑换货币</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem2]</t>
+  </si>
+  <si>
+    <t>灵晶体</t>
+  </si>
+  <si>
+    <t>菱形晶体内部闪耀着变幻莫测的色彩，可以兑换中量灵晶币。</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem3]</t>
+  </si>
+  <si>
+    <t>灵晶完全体</t>
+  </si>
+  <si>
+    <t>菱形晶体内部闪耀着变幻莫测的色彩，可以兑换大量灵晶币。</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem4]</t>
+  </si>
+  <si>
     <t>翡翠木枝</t>
   </si>
   <si>
@@ -120,250 +170,134 @@
     <t>汲取了近千年灵能的枝条，金色叶片象征着永不枯萎的极致生命法则。</t>
   </si>
   <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1002]</t>
+  </si>
+  <si>
     <t>碧葛垂硬木</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>翡翠林海</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1002]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碧葛垂的低部枝干硬化木材，拥有奇特的年轮结构。</t>
+  </si>
+  <si>
+    <t>装备锻造</t>
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1003]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>碧葛垂银木</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碧葛垂的中部枝干稀有木材，散发着幽蓝色冷光。</t>
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1004]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>碧葛垂圣木</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碧葛垂极高的树冠尖端，被纯粹的“灵域之光”浸润了数千年。</t>
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1005]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>灵光棉绒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>碧葛垂的低部枝干硬化木材，拥有奇特的年轮结构。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>碧葛垂的中部枝干稀有木材，散发着幽蓝色冷光。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>碧葛垂极高的树冠尖端，被纯粹的“灵域之光”浸润了数千年。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>棉绒中心凝聚着微小的灵能晶体，使其散发出轻微的银白色光芒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1006]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵光紫绒</t>
   </si>
   <si>
     <t>内部充满了一种不稳定的、扭曲的灵能，这种灵能极难被驯服和提纯。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>制作药剂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1007]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>灵光紫绒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>灵光金绒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>纤维团呈温暖的亮金色，在迷雾中也能持续散发出清晰可见的微光。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1008]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>usable</t>
-  </si>
-  <si>
-    <t>可使用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵能铜矿</t>
+  </si>
+  <si>
+    <t>吸收少量灵能后浑然天成的铜矿，可用于装备锻造。</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1009]</t>
+  </si>
+  <si>
+    <t>灵能银矿</t>
+  </si>
+  <si>
+    <t>吸收中量灵能后浑然天成的银矿，可用于装备锻造。</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1010]</t>
+  </si>
+  <si>
+    <t>灵能钻石矿</t>
+  </si>
+  <si>
+    <t>吸收大量灵能后浑然天成的钻石矿，可用于装备锻造</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1011]</t>
+  </si>
+  <si>
+    <t>林海银匣</t>
   </si>
   <si>
     <t>从翡翠林海中获取的战利品，使用后随机获得各种道具。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>抽奖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem10000]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林海金匣</t>
+  </si>
+  <si>
+    <t>从翡翠林海中获取的稀有战利品，使用后有机会获得稀有道具。</t>
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem10001]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林海宝匣</t>
+  </si>
+  <si>
+    <t>从翡翠林海中获取的臻稀战利品，使用后大概率获得珍贵道具。</t>
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem10002]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林海银匣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林海金匣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林海宝匣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从翡翠林海中获取的稀有战利品，使用后有机会获得稀有道具。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从翡翠林海中获取的臻稀战利品，使用后大概率获得珍贵道具。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>level</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物品品阶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>灵晶微体</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广泛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兑换货币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem2]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>灵晶体</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem3]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>灵晶完全体</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem4]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>灵能铜矿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>灵能银矿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>灵能钻石矿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吸收少量灵能后浑然天成的铜矿，可用于装备锻造。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>菱形晶体内部闪耀着变幻莫测的色彩，可以兑换少量灵晶币。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>菱形晶体内部闪耀着变幻莫测的色彩，可以兑换中量灵晶币。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>菱形晶体内部闪耀着变幻莫测的色彩，可以兑换大量灵晶币。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>装备锻造</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主要用途</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吸收中量灵能后浑然天成的银矿，可用于装备锻造。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吸收大量灵能后浑然天成的钻石矿，可用于装备锻造</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1009]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1010]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1011]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -372,29 +306,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -402,9 +659,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -412,27 +911,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -690,25 +1233,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="60.44140625" customWidth="1"/>
-    <col min="5" max="5" width="7.21875" customWidth="1"/>
-    <col min="7" max="7" width="11.77734375" customWidth="1"/>
-    <col min="8" max="8" width="43.5546875" customWidth="1"/>
-    <col min="9" max="9" width="8.44140625" customWidth="1"/>
+    <col min="2" max="2" width="7.10833333333333" customWidth="1"/>
+    <col min="3" max="3" width="13.4416666666667" customWidth="1"/>
+    <col min="4" max="4" width="60.4416666666667" customWidth="1"/>
+    <col min="5" max="5" width="7.21666666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.775" customWidth="1"/>
+    <col min="8" max="8" width="43.5583333333333" customWidth="1"/>
+    <col min="9" max="9" width="8.44166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -733,691 +1276,691 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>33</v>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>20</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>78</v>
+      <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="E5">
         <v>500</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2">
+      <c r="F5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="B6">
         <v>3</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>79</v>
+      <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="E6">
         <v>2000</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2">
+      <c r="F6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="B7">
         <v>4</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>80</v>
+      <c r="C7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="E7">
         <v>10000</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="F7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="8" ht="28.5" spans="1:11">
       <c r="B8">
         <v>1000</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E8">
         <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>0</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="B9">
         <v>1001</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>42</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E9">
         <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
+        <v>44</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
         <v>0</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="B10">
         <v>1002</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>45</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="E10">
         <v>1248</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>0</v>
       </c>
       <c r="K10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11">
       <c r="B11">
         <v>1003</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>29</v>
+      <c r="C11" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E11">
         <v>34</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>30</v>
+      <c r="F11" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>0</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11">
       <c r="B12">
         <v>1004</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>35</v>
+      <c r="C12" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E12">
         <v>168</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>30</v>
+      <c r="F12" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <v>0</v>
       </c>
       <c r="K12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11">
       <c r="B13">
         <v>1005</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>37</v>
+      <c r="C13" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E13">
         <v>1799</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>30</v>
+      <c r="F13" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <v>0</v>
       </c>
       <c r="K13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11">
       <c r="B14">
         <v>1006</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>39</v>
+      <c r="C14" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E14">
         <v>18</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>30</v>
+      <c r="F14" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="1">
         <v>0</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="B15">
         <v>1007</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>48</v>
+      <c r="C15" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E15">
         <v>150</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>47</v>
+      <c r="F15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="1">
         <v>0</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11">
       <c r="B16">
         <v>1008</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>49</v>
+      <c r="C16" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E16">
         <v>1568</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>51</v>
+      <c r="F16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <v>0</v>
       </c>
       <c r="K16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11">
       <c r="B17">
         <v>1009</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>74</v>
+      <c r="C17" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E17">
         <v>50</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>30</v>
+      <c r="F17" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>85</v>
+        <v>50</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="1">
         <v>0</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11">
       <c r="B18">
         <v>1010</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>75</v>
+      <c r="C18" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E18">
         <v>200</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>30</v>
+      <c r="F18" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="1">
         <v>0</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11">
       <c r="B19">
         <v>1011</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>76</v>
+      <c r="C19" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E19">
         <v>2000</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>30</v>
+      <c r="F19" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>87</v>
+        <v>50</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="1">
         <v>0</v>
       </c>
       <c r="K19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11">
       <c r="B20">
         <v>10000</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>59</v>
+      <c r="C20" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>30</v>
+      <c r="F20" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="1">
         <v>1</v>
       </c>
       <c r="K20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11">
       <c r="B21">
         <v>10001</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>60</v>
+      <c r="C21" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>30</v>
+      <c r="F21" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>57</v>
+        <v>78</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="1">
         <v>1</v>
       </c>
       <c r="K21">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11">
       <c r="B22">
         <v>10002</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>63</v>
+      <c r="C22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>30</v>
+      <c r="F22" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>58</v>
+        <v>78</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="1">
         <v>1</v>
       </c>
       <c r="K22">
@@ -1425,7 +1968,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="103">
   <si>
     <t>##var</t>
   </si>
@@ -255,6 +255,57 @@
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1011]</t>
+  </si>
+  <si>
+    <t>低级红药剂</t>
+  </si>
+  <si>
+    <t>药剂</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem3000]</t>
+  </si>
+  <si>
+    <t>试炼长剑</t>
+  </si>
+  <si>
+    <t>系统发放</t>
+  </si>
+  <si>
+    <t>穿戴</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem4000]</t>
+  </si>
+  <si>
+    <t>试炼头盔</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem5000]</t>
+  </si>
+  <si>
+    <t>试炼胸甲</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem6000]</t>
+  </si>
+  <si>
+    <t>试炼灵珠</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem7000]</t>
+  </si>
+  <si>
+    <t>试炼腿甲</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem8000]</t>
+  </si>
+  <si>
+    <t>试炼鞋子</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem9000]</t>
   </si>
   <si>
     <t>林海银匣</t>
@@ -297,14 +348,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -777,133 +821,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -911,13 +955,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1239,7 +1283,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="7.10833333333333" customWidth="1"/>
@@ -1873,97 +1917,321 @@
     </row>
     <row r="20" spans="2:11">
       <c r="B20">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="I20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="1">
         <v>1</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:11">
       <c r="B21">
-        <v>10001</v>
+        <v>4000</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>82</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:11">
       <c r="B22">
-        <v>10002</v>
+        <v>5000</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="B23">
+        <v>6000</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="B24">
+        <v>7000</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11">
+      <c r="B25">
+        <v>8000</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11">
+      <c r="B26">
+        <v>9000</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11">
+      <c r="B27">
+        <v>10000</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22">
+      <c r="G27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="B28">
+        <v>10001</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11">
+      <c r="B29">
+        <v>10002</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
+      <c r="K29">
         <v>3</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\Cyber\Demo-Cyber\MiniTemplate\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FF26A8-2322-45A6-8127-1A5FCED6A75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28785" windowHeight="12975"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="117">
   <si>
     <t>##var</t>
   </si>
@@ -336,19 +340,69 @@
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem10002]</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>armorPenetration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破甲值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defense</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>damageAvoidance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>免伤值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,345 +411,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -703,323 +441,34 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1277,25 +726,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.10833333333333" customWidth="1"/>
-    <col min="3" max="3" width="13.4416666666667" customWidth="1"/>
-    <col min="4" max="4" width="60.4416666666667" customWidth="1"/>
-    <col min="5" max="5" width="7.21666666666667" customWidth="1"/>
-    <col min="7" max="7" width="11.775" customWidth="1"/>
-    <col min="8" max="8" width="43.5583333333333" customWidth="1"/>
-    <col min="9" max="9" width="8.44166666666667" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="60.44140625" customWidth="1"/>
+    <col min="5" max="5" width="7.21875" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" customWidth="1"/>
+    <col min="8" max="8" width="43.5546875" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1320,17 +770,35 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1355,17 +823,35 @@
       <c r="H2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1399,8 +885,26 @@
       <c r="K3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1419,126 +923,144 @@
       <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>21</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>27</v>
       </c>
       <c r="E5">
         <v>500</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>3</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>32</v>
       </c>
       <c r="E6">
         <v>2000</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>4</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>35</v>
       </c>
       <c r="E7">
         <v>10000</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="28.5" spans="1:11">
+    <row r="8" spans="1:17" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1000</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E8">
@@ -1547,7 +1069,7 @@
       <c r="F8" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="1" t="s">
         <v>40</v>
       </c>
       <c r="H8" t="s">
@@ -1556,21 +1078,21 @@
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1001</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E9">
@@ -1579,30 +1101,30 @@
       <c r="F9" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="1" t="s">
         <v>40</v>
       </c>
       <c r="H9" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:17" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1002</v>
       </c>
       <c r="C10" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E10">
@@ -1611,624 +1133,660 @@
       <c r="F10" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" t="s">
         <v>47</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1003</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E11">
         <v>34</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" t="s">
         <v>51</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>1004</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E12">
         <v>168</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" t="s">
         <v>54</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>1005</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E13">
         <v>1799</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" t="s">
         <v>57</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>1006</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E14">
         <v>18</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" t="s">
         <v>60</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:17" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>1007</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E15">
         <v>150</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" t="s">
         <v>63</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:17" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1008</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E16">
         <v>1568</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" t="s">
         <v>66</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:11">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>1009</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E17">
         <v>50</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" t="s">
         <v>69</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:11">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>1010</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="1" t="s">
         <v>71</v>
       </c>
       <c r="E18">
         <v>200</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" t="s">
         <v>72</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:11">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>1011</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="1" t="s">
         <v>74</v>
       </c>
       <c r="E19">
         <v>2000</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" t="s">
         <v>39</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" t="s">
         <v>75</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:11">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>3000</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E20">
         <v>10</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" t="s">
         <v>78</v>
       </c>
       <c r="I20">
         <v>2</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20">
         <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:11">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>4000</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" t="s">
         <v>80</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" t="s">
         <v>82</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="2:11">
+      <c r="L21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>5000</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="1" t="s">
         <v>83</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" t="s">
         <v>80</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" t="s">
         <v>84</v>
       </c>
       <c r="I22">
         <v>1</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="2:11">
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>6</v>
+      </c>
+      <c r="Q22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>6000</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="1" t="s">
         <v>85</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" t="s">
         <v>80</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" t="s">
         <v>86</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:11">
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>7000</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" t="s">
         <v>80</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" t="s">
         <v>88</v>
       </c>
       <c r="I24">
         <v>1</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:11">
+      <c r="L24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>8000</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="1" t="s">
         <v>89</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" t="s">
         <v>80</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" t="s">
         <v>90</v>
       </c>
       <c r="I25">
         <v>1</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="2:11">
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="P25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>9000</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>91</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="1" t="s">
         <v>91</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" t="s">
         <v>80</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" t="s">
         <v>92</v>
       </c>
       <c r="I26">
         <v>1</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="2:11">
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>4</v>
+      </c>
+      <c r="Q26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>10000</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="1" t="s">
         <v>94</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" t="s">
         <v>39</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" t="s">
         <v>96</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27">
         <v>1</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:11">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>10001</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>97</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" t="s">
         <v>39</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" t="s">
         <v>99</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28">
         <v>1</v>
       </c>
       <c r="K28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:11">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>10002</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>100</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" t="s">
         <v>101</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" t="s">
         <v>39</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" t="s">
         <v>102</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29">
         <v>1</v>
       </c>
       <c r="K29">
@@ -2236,7 +1794,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\Cyber\Demo-Cyber\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FF26A8-2322-45A6-8127-1A5FCED6A75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4620C1-E3E9-4984-BF82-3F6FDCFF203E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="125">
   <si>
     <t>##var</t>
   </si>
@@ -395,6 +395,38 @@
   </si>
   <si>
     <t>魔力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sm</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -732,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.109375" customWidth="1"/>
@@ -745,7 +777,7 @@
     <col min="12" max="12" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -797,8 +829,20 @@
       <c r="Q1" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -850,8 +894,20 @@
       <c r="Q2" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -903,8 +959,20 @@
       <c r="Q3" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -956,8 +1024,20 @@
       <c r="Q4" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2</v>
       </c>
@@ -989,7 +1069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>3</v>
       </c>
@@ -1021,7 +1101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>4</v>
       </c>
@@ -1053,7 +1133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1000</v>
       </c>
@@ -1085,7 +1165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1001</v>
       </c>
@@ -1117,7 +1197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1002</v>
       </c>
@@ -1149,7 +1229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1003</v>
       </c>
@@ -1181,7 +1261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>1004</v>
       </c>
@@ -1213,7 +1293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>1005</v>
       </c>
@@ -1245,7 +1325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>1006</v>
       </c>
@@ -1277,7 +1357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>1007</v>
       </c>
@@ -1309,7 +1389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1008</v>
       </c>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\Cyber\Demo-Cyber\MiniTemplate\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4620C1-E3E9-4984-BF82-3F6FDCFF203E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="123">
   <si>
     <t>##var</t>
   </si>
@@ -66,6 +62,36 @@
     <t>level</t>
   </si>
   <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>armorPenetration</t>
+  </si>
+  <si>
+    <t>defense</t>
+  </si>
+  <si>
+    <t>damageAvoidance</t>
+  </si>
+  <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>mp</t>
+  </si>
+  <si>
+    <t>cp</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>sp</t>
+  </si>
+  <si>
+    <t>sm</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -75,6 +101,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -111,6 +140,33 @@
     <t>物品品阶</t>
   </si>
   <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>破甲值</t>
+  </si>
+  <si>
+    <t>防御力</t>
+  </si>
+  <si>
+    <t>免伤值</t>
+  </si>
+  <si>
+    <t>生命值</t>
+  </si>
+  <si>
+    <t>魔力值</t>
+  </si>
+  <si>
+    <t>暴击率</t>
+  </si>
+  <si>
+    <t>暴击倍率</t>
+  </si>
+  <si>
+    <t>吸血率</t>
+  </si>
+  <si>
     <t>灵晶微体</t>
   </si>
   <si>
@@ -270,7 +326,7 @@
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem3000]</t>
   </si>
   <si>
-    <t>试炼长剑</t>
+    <t>试炼灵武</t>
   </si>
   <si>
     <t>系统发放</t>
@@ -340,101 +396,19 @@
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem10002]</t>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c,s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>armorPenetration</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>破甲值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>defense</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>damageAvoidance</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>免伤值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔力值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击倍率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吸血率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,29 +417,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -473,9 +770,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -483,24 +1022,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -758,26 +1341,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:U29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="60.44140625" customWidth="1"/>
-    <col min="5" max="5" width="7.21875" customWidth="1"/>
-    <col min="7" max="7" width="11.77734375" customWidth="1"/>
-    <col min="8" max="8" width="43.5546875" customWidth="1"/>
-    <col min="9" max="9" width="8.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="7.10833333333333" customWidth="1"/>
+    <col min="3" max="3" width="13.4416666666667" customWidth="1"/>
+    <col min="4" max="4" width="60.4416666666667" customWidth="1"/>
+    <col min="5" max="5" width="7.21666666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.775" customWidth="1"/>
+    <col min="8" max="8" width="43.5583333333333" customWidth="1"/>
+    <col min="9" max="9" width="8.44166666666667" customWidth="1"/>
+    <col min="12" max="12" width="12.5583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -811,253 +1394,253 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J4" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E5">
         <v>500</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1069,27 +1652,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21">
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="E6">
         <v>2000</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1101,27 +1684,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21">
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E7">
         <v>10000</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1133,27 +1716,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="8" ht="28.5" spans="1:21">
       <c r="B8">
         <v>1000</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="E8">
         <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="H8" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1165,27 +1748,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21">
       <c r="B9">
         <v>1001</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>62</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="E9">
         <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1197,27 +1780,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21">
       <c r="B10">
         <v>1002</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>46</v>
+        <v>65</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E10">
         <v>1248</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1229,27 +1812,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21">
       <c r="B11">
         <v>1003</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="E11">
         <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="H11" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1261,27 +1844,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21">
       <c r="B12">
         <v>1004</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>72</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="E12">
         <v>168</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="H12" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1293,27 +1876,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21">
       <c r="B13">
         <v>1005</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="E13">
         <v>1799</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="H13" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1325,27 +1908,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21">
       <c r="B14">
         <v>1006</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>59</v>
+        <v>78</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="E14">
         <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="H14" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1357,27 +1940,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21">
       <c r="B15">
         <v>1007</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>81</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="E15">
         <v>150</v>
       </c>
       <c r="F15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="H15" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1389,27 +1972,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21">
       <c r="B16">
         <v>1008</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>65</v>
+        <v>84</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="E16">
         <v>1568</v>
       </c>
       <c r="F16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="H16" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1421,27 +2004,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17">
       <c r="B17">
         <v>1009</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>68</v>
+        <v>87</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="E17">
         <v>50</v>
       </c>
       <c r="F17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="H17" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1453,27 +2036,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17">
       <c r="B18">
         <v>1010</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="E18">
         <v>200</v>
       </c>
       <c r="F18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1485,27 +2068,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17">
       <c r="B19">
         <v>1011</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>74</v>
+        <v>93</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="E19">
         <v>2000</v>
       </c>
       <c r="F19" t="s">
-        <v>39</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="H19" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1517,27 +2100,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17">
       <c r="B20">
         <v>3000</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="E20">
         <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>77</v>
+        <v>59</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="H20" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -1549,27 +2132,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17">
       <c r="B21">
         <v>4000</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>79</v>
+        <v>99</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>80</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>81</v>
+        <v>100</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="H21" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -1584,27 +2167,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17">
       <c r="B22">
         <v>5000</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>83</v>
+        <v>103</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>80</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>81</v>
+        <v>100</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="H22" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -1625,27 +2208,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17">
       <c r="B23">
         <v>6000</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>85</v>
+        <v>105</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>81</v>
+        <v>100</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="H23" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -1663,27 +2246,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17">
       <c r="B24">
         <v>7000</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>87</v>
+        <v>107</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>80</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>81</v>
+        <v>100</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="H24" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -1698,27 +2281,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17">
       <c r="B25">
         <v>8000</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>89</v>
+        <v>109</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>80</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>81</v>
+        <v>100</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="H25" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="I25">
         <v>1</v>
@@ -1736,27 +2319,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17">
       <c r="B26">
         <v>9000</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>91</v>
+        <v>111</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>80</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>81</v>
+        <v>100</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="H26" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="I26">
         <v>1</v>
@@ -1777,27 +2360,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17">
       <c r="B27">
         <v>10000</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>94</v>
+        <v>113</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>39</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>95</v>
+        <v>59</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="H27" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1809,27 +2392,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17">
       <c r="B28">
         <v>10001</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>98</v>
+        <v>117</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>39</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>95</v>
+        <v>59</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="H28" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1841,27 +2424,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17">
       <c r="B29">
         <v>10002</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>39</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>95</v>
+        <v>59</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="H29" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1874,7 +2457,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960"/>
+    <workbookView windowWidth="28785" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="127">
   <si>
     <t>##var</t>
   </si>
@@ -396,6 +396,18 @@
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem10002]</t>
+  </si>
+  <si>
+    <t>白狒狒灵环</t>
+  </si>
+  <si>
+    <t>白狒狒的灵环，封存着远古的力量</t>
+  </si>
+  <si>
+    <t>怪物掉落</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem20000]</t>
   </si>
 </sst>
 </file>
@@ -408,14 +420,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -888,133 +893,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1022,7 +1027,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1347,7 +1352,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="7.10833333333333" customWidth="1"/>
@@ -2004,7 +2009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:17">
+    <row r="17" spans="2:19">
       <c r="B17">
         <v>1009</v>
       </c>
@@ -2036,7 +2041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:17">
+    <row r="18" spans="2:19">
       <c r="B18">
         <v>1010</v>
       </c>
@@ -2068,7 +2073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:19">
       <c r="B19">
         <v>1011</v>
       </c>
@@ -2100,7 +2105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:17">
+    <row r="20" spans="2:19">
       <c r="B20">
         <v>3000</v>
       </c>
@@ -2132,7 +2137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:19">
       <c r="B21">
         <v>4000</v>
       </c>
@@ -2167,7 +2172,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:19">
       <c r="B22">
         <v>5000</v>
       </c>
@@ -2208,7 +2213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:19">
       <c r="B23">
         <v>6000</v>
       </c>
@@ -2246,7 +2251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:19">
       <c r="B24">
         <v>7000</v>
       </c>
@@ -2281,7 +2286,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:19">
       <c r="B25">
         <v>8000</v>
       </c>
@@ -2319,7 +2324,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:19">
       <c r="B26">
         <v>9000</v>
       </c>
@@ -2360,7 +2365,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:19">
       <c r="B27">
         <v>10000</v>
       </c>
@@ -2392,7 +2397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:19">
       <c r="B28">
         <v>10001</v>
       </c>
@@ -2424,7 +2429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:19">
       <c r="B29">
         <v>10002</v>
       </c>
@@ -2454,6 +2459,60 @@
       </c>
       <c r="K29">
         <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19">
+      <c r="B30">
+        <v>20000</v>
+      </c>
+      <c r="C30" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" t="s">
+        <v>124</v>
+      </c>
+      <c r="E30">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H30" t="s">
+        <v>126</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>10</v>
+      </c>
+      <c r="M30"/>
+      <c r="N30">
+        <v>5</v>
+      </c>
+      <c r="O30">
+        <v>1</v>
+      </c>
+      <c r="P30">
+        <v>15</v>
+      </c>
+      <c r="Q30">
+        <v>5</v>
+      </c>
+      <c r="R30">
+        <v>1</v>
+      </c>
+      <c r="S30">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="170">
   <si>
     <t>##var</t>
   </si>
@@ -92,6 +92,9 @@
     <t>sm</t>
   </si>
   <si>
+    <t>obtain</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -167,6 +170,12 @@
     <t>吸血率</t>
   </si>
   <si>
+    <t>吸血倍率</t>
+  </si>
+  <si>
+    <t>使用后获得物品 (id, num, weight)</t>
+  </si>
+  <si>
     <t>灵晶微体</t>
   </si>
   <si>
@@ -311,7 +320,7 @@
     <t>灵能钻石矿</t>
   </si>
   <si>
-    <t>吸收大量灵能后浑然天成的钻石矿，可用于装备锻造</t>
+    <t>吸收大量灵能后浑然天成的钻石矿，可用于装备锻造。</t>
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem1011]</t>
@@ -329,6 +338,9 @@
     <t>试炼灵武</t>
   </si>
   <si>
+    <t>试炼灵武，具有微弱的攻击力。</t>
+  </si>
+  <si>
     <t>系统发放</t>
   </si>
   <si>
@@ -338,36 +350,126 @@
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem4000]</t>
   </si>
   <si>
+    <t>灵能铜剑</t>
+  </si>
+  <si>
+    <t>剑身由灵能铜矿铸造而成，一把适用于初级猎兽者的武器。</t>
+  </si>
+  <si>
+    <t>锻造</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem4001]</t>
+  </si>
+  <si>
+    <t>白银巨剑</t>
+  </si>
+  <si>
+    <t>剑身由灵能银矿铸造而成，表面流转如水般的翡翠色纹路。</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem4002]</t>
+  </si>
+  <si>
     <t>试炼头盔</t>
   </si>
   <si>
+    <t>试炼头盔，具有微弱的防御力。</t>
+  </si>
+  <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem5000]</t>
   </si>
   <si>
+    <t>灵能铜盔</t>
+  </si>
+  <si>
+    <t>由灵能铜矿铸造而成，具有不错的防御力。</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem5001]</t>
+  </si>
+  <si>
+    <t>灵能银盔</t>
+  </si>
+  <si>
+    <t>由灵能银矿铸造而成，具有不错的防御力。</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem5002]</t>
+  </si>
+  <si>
     <t>试炼胸甲</t>
   </si>
   <si>
+    <t>试炼胸甲，具有微弱的防御力。</t>
+  </si>
+  <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem6000]</t>
   </si>
   <si>
+    <t>灵能铜甲</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem6001]</t>
+  </si>
+  <si>
+    <t>灵能银甲</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem6002]</t>
+  </si>
+  <si>
     <t>试炼灵珠</t>
   </si>
   <si>
+    <t>一阶灵珠，可以使用矿石升级。</t>
+  </si>
+  <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem7000]</t>
   </si>
   <si>
     <t>试炼腿甲</t>
   </si>
   <si>
+    <t>试炼腿甲，具有微弱的防御力。</t>
+  </si>
+  <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem8000]</t>
   </si>
   <si>
+    <t>灵能铜护腿</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem8001]</t>
+  </si>
+  <si>
+    <t>灵能银护腿</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem8002]</t>
+  </si>
+  <si>
     <t>试炼鞋子</t>
   </si>
   <si>
+    <t>试炼鞋子，具有微弱的防御力。</t>
+  </si>
+  <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem9000]</t>
   </si>
   <si>
+    <t>灵能铜靴</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem9001]</t>
+  </si>
+  <si>
+    <t>灵能银靴</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem9002]</t>
+  </si>
+  <si>
     <t>林海银匣</t>
   </si>
   <si>
@@ -380,6 +482,9 @@
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem10000]</t>
   </si>
   <si>
+    <t>1002,1,100|1005,1,100|1008,1,100|2,1,1000|1009,1,1000</t>
+  </si>
+  <si>
     <t>林海金匣</t>
   </si>
   <si>
@@ -389,6 +494,9 @@
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem10001]</t>
   </si>
   <si>
+    <t>1002,1,200|1005,1,200|1008,1,200|2,1,200|3,1,100|1009,1,200|1010,1,100</t>
+  </si>
+  <si>
     <t>林海宝匣</t>
   </si>
   <si>
@@ -398,6 +506,9 @@
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem10002]</t>
   </si>
   <si>
+    <t>1002,1,1000|1005,1,1000|1008,1,1000|2,2,1000|3,1,1000|4,1,100|1009,2,1000|1010,1,1000|1011,1,100</t>
+  </si>
+  <si>
     <t>白狒狒灵环</t>
   </si>
   <si>
@@ -408,6 +519,24 @@
   </si>
   <si>
     <t>Assets/UI/Items/Items.spriteatlas[SpriteItem20000]</t>
+  </si>
+  <si>
+    <t>古石巨人灵环</t>
+  </si>
+  <si>
+    <t>古石巨人的灵环，封存着远古的力量</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem20001]</t>
+  </si>
+  <si>
+    <t>青石巨人灵环</t>
+  </si>
+  <si>
+    <t>青石巨人的灵环，封存者远古的力量</t>
+  </si>
+  <si>
+    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem20002]</t>
   </si>
 </sst>
 </file>
@@ -1352,7 +1481,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="7.10833333333333" customWidth="1"/>
@@ -1363,9 +1492,10 @@
     <col min="8" max="8" width="43.5583333333333" customWidth="1"/>
     <col min="9" max="9" width="8.44166666666667" customWidth="1"/>
     <col min="12" max="12" width="12.5583333333333" customWidth="1"/>
+    <col min="22" max="22" width="82.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1429,223 +1559,235 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21">
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21">
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21">
+        <v>27</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21">
+        <v>47</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E5">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1657,27 +1799,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:22">
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6">
+        <v>500</v>
+      </c>
+      <c r="F6" t="s">
         <v>51</v>
       </c>
-      <c r="D6" t="s">
+      <c r="G6" t="s">
         <v>52</v>
       </c>
-      <c r="E6">
-        <v>2000</v>
-      </c>
-      <c r="F6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" t="s">
-        <v>49</v>
-      </c>
       <c r="H6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1689,27 +1831,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:22">
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E7">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1721,27 +1863,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="28.5" spans="1:21">
+    <row r="8" ht="28.5" spans="1:22">
       <c r="B8">
         <v>1000</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1753,27 +1895,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:22">
       <c r="B9">
         <v>1001</v>
       </c>
       <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="H9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1785,27 +1927,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:22">
       <c r="B10">
         <v>1002</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E10">
-        <v>1248</v>
+        <v>102</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1817,27 +1959,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:22">
       <c r="B11">
         <v>1003</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E11">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1849,27 +1991,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:22">
       <c r="B12">
         <v>1004</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12">
+        <v>24</v>
+      </c>
+      <c r="F12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E12">
-        <v>168</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1881,27 +2023,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:22">
       <c r="B13">
         <v>1005</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E13">
-        <v>1799</v>
+        <v>106</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1913,27 +2055,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:22">
       <c r="B14">
         <v>1006</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1945,27 +2087,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:22">
       <c r="B15">
         <v>1007</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E15">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1977,27 +2119,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:22">
       <c r="B16">
         <v>1008</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E16">
-        <v>1568</v>
+        <v>110</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2014,22 +2156,22 @@
         <v>1009</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E17">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -2046,22 +2188,22 @@
         <v>1010</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E18">
-        <v>200</v>
+        <v>98</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -2078,22 +2220,22 @@
         <v>1011</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E19">
-        <v>2000</v>
+        <v>511</v>
       </c>
       <c r="F19" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -2110,22 +2252,22 @@
         <v>3000</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H20" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -2142,22 +2284,22 @@
         <v>4000</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H21" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -2174,25 +2316,25 @@
     </row>
     <row r="22" spans="2:19">
       <c r="B22">
-        <v>5000</v>
+        <v>4001</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H22" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -2201,39 +2343,39 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>1</v>
-      </c>
-      <c r="P22">
-        <v>6</v>
-      </c>
-      <c r="Q22">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>20</v>
+      </c>
+      <c r="R22">
+        <v>5</v>
+      </c>
+      <c r="S22">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="2:19">
       <c r="B23">
-        <v>6000</v>
+        <v>4002</v>
       </c>
       <c r="C23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23">
+        <v>200</v>
+      </c>
+      <c r="F23" t="s">
+        <v>109</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="H23" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -2242,36 +2384,42 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>1</v>
-      </c>
-      <c r="P23">
+        <v>2</v>
+      </c>
+      <c r="L23">
+        <v>30</v>
+      </c>
+      <c r="M23">
+        <v>5</v>
+      </c>
+      <c r="R23">
         <v>10</v>
+      </c>
+      <c r="S23">
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="2:19">
       <c r="B24">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H24" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -2282,31 +2430,37 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24">
-        <v>10</v>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>8</v>
+      </c>
+      <c r="Q24">
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="2:19">
       <c r="B25">
-        <v>8000</v>
+        <v>5001</v>
       </c>
       <c r="C25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25">
+        <v>50</v>
+      </c>
+      <c r="F25" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25" t="s">
-        <v>100</v>
-      </c>
       <c r="G25" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H25" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I25">
         <v>1</v>
@@ -2315,36 +2469,39 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P25">
         <v>10</v>
       </c>
+      <c r="Q25">
+        <v>6</v>
+      </c>
     </row>
     <row r="26" spans="2:19">
       <c r="B26">
-        <v>9000</v>
+        <v>5002</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="F26" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H26" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="I26">
         <v>1</v>
@@ -2353,138 +2510,156 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P26">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q26">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="2:19">
       <c r="B27">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="H27" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="P27">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="2:19">
       <c r="B28">
-        <v>10001</v>
+        <v>6001</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F28" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="H28" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="N28">
         <v>2</v>
+      </c>
+      <c r="P28">
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="2:19">
       <c r="B29">
-        <v>10002</v>
+        <v>6002</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
-      </c>
-      <c r="D29" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>121</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F29" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="H29" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29">
+        <v>2</v>
+      </c>
+      <c r="N29">
         <v>3</v>
+      </c>
+      <c r="P29">
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="2:19">
       <c r="B30">
-        <v>20000</v>
+        <v>7000</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30" t="s">
-        <v>124</v>
+        <v>130</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>59</v>
-      </c>
-      <c r="G30" t="s">
-        <v>125</v>
+        <v>104</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="H30" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -2495,24 +2670,508 @@
       <c r="L30">
         <v>10</v>
       </c>
-      <c r="M30"/>
-      <c r="N30">
+    </row>
+    <row r="31" spans="2:19">
+      <c r="B31">
+        <v>8000</v>
+      </c>
+      <c r="C31" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31" t="s">
+        <v>104</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H31" t="s">
+        <v>135</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="P31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19">
+      <c r="B32">
+        <v>8001</v>
+      </c>
+      <c r="C32" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32">
+        <v>50</v>
+      </c>
+      <c r="F32" t="s">
+        <v>109</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H32" t="s">
+        <v>137</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="N32">
+        <v>2</v>
+      </c>
+      <c r="P32">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22">
+      <c r="B33">
+        <v>8002</v>
+      </c>
+      <c r="C33" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33">
+        <v>200</v>
+      </c>
+      <c r="F33" t="s">
+        <v>109</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H33" t="s">
+        <v>139</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="N33">
+        <v>3</v>
+      </c>
+      <c r="P33">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22">
+      <c r="B34">
+        <v>9000</v>
+      </c>
+      <c r="C34" t="s">
+        <v>140</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34" t="s">
+        <v>104</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H34" t="s">
+        <v>142</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="P34">
+        <v>4</v>
+      </c>
+      <c r="Q34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22">
+      <c r="B35">
+        <v>9001</v>
+      </c>
+      <c r="C35" t="s">
+        <v>143</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E35">
+        <v>50</v>
+      </c>
+      <c r="F35" t="s">
+        <v>109</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H35" t="s">
+        <v>144</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>2</v>
+      </c>
+      <c r="P35">
+        <v>6</v>
+      </c>
+      <c r="Q35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="2:22">
+      <c r="B36">
+        <v>9002</v>
+      </c>
+      <c r="C36" t="s">
+        <v>145</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E36">
+        <v>200</v>
+      </c>
+      <c r="F36" t="s">
+        <v>109</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H36" t="s">
+        <v>146</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>2</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="P36">
+        <v>8</v>
+      </c>
+      <c r="Q36">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22">
+      <c r="B37">
+        <v>10000</v>
+      </c>
+      <c r="C37" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H37" t="s">
+        <v>150</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="V37" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="38" spans="2:22">
+      <c r="B38">
+        <v>10001</v>
+      </c>
+      <c r="C38" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38" t="s">
+        <v>62</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H38" t="s">
+        <v>154</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>2</v>
+      </c>
+      <c r="V38" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22">
+      <c r="B39">
+        <v>10002</v>
+      </c>
+      <c r="C39" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39" t="s">
+        <v>62</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H39" t="s">
+        <v>158</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>3</v>
+      </c>
+      <c r="V39" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="2:22">
+      <c r="B40">
+        <v>20000</v>
+      </c>
+      <c r="C40" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40">
+        <v>20</v>
+      </c>
+      <c r="F40" t="s">
+        <v>62</v>
+      </c>
+      <c r="G40" t="s">
+        <v>162</v>
+      </c>
+      <c r="H40" t="s">
+        <v>163</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>10</v>
+      </c>
+      <c r="N40">
         <v>5</v>
       </c>
-      <c r="O30">
-        <v>1</v>
-      </c>
-      <c r="P30">
+      <c r="O40">
+        <v>1</v>
+      </c>
+      <c r="P40">
         <v>15</v>
       </c>
-      <c r="Q30">
+      <c r="Q40">
         <v>5</v>
       </c>
-      <c r="R30">
-        <v>1</v>
-      </c>
-      <c r="S30">
+      <c r="R40">
+        <v>1</v>
+      </c>
+      <c r="S40">
         <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="2:22">
+      <c r="B41">
+        <v>20001</v>
+      </c>
+      <c r="C41" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" t="s">
+        <v>165</v>
+      </c>
+      <c r="E41">
+        <v>20</v>
+      </c>
+      <c r="F41" t="s">
+        <v>62</v>
+      </c>
+      <c r="G41" t="s">
+        <v>162</v>
+      </c>
+      <c r="H41" t="s">
+        <v>166</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>20</v>
+      </c>
+      <c r="N41">
+        <v>10</v>
+      </c>
+      <c r="O41">
+        <v>2</v>
+      </c>
+      <c r="P41">
+        <v>20</v>
+      </c>
+      <c r="Q41">
+        <v>5</v>
+      </c>
+      <c r="R41">
+        <v>1</v>
+      </c>
+      <c r="S41">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22">
+      <c r="B42">
+        <v>20002</v>
+      </c>
+      <c r="C42" t="s">
+        <v>167</v>
+      </c>
+      <c r="D42" t="s">
+        <v>168</v>
+      </c>
+      <c r="E42">
+        <v>20</v>
+      </c>
+      <c r="F42" t="s">
+        <v>62</v>
+      </c>
+      <c r="G42" t="s">
+        <v>162</v>
+      </c>
+      <c r="H42" t="s">
+        <v>169</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>2</v>
+      </c>
+      <c r="L42">
+        <v>30</v>
+      </c>
+      <c r="N42">
+        <v>10</v>
+      </c>
+      <c r="O42">
+        <v>3</v>
+      </c>
+      <c r="P42">
+        <v>30</v>
+      </c>
+      <c r="Q42">
+        <v>5</v>
+      </c>
+      <c r="R42"/>
+      <c r="S42"/>
+      <c r="T42">
+        <v>1</v>
+      </c>
+      <c r="U42">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
